--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-context-extension</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-context-extension</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,7 +334,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr)
+    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr)
 </t>
   </si>
   <si>
@@ -676,7 +676,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.22265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="89.96484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-context-extension</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-context-extension</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,7 +334,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr)
+    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr)
 </t>
   </si>
   <si>
@@ -676,7 +676,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.96484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.22265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-context-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Appointment</t>
   </si>
   <si>
     <t>ID</t>
